--- a/backend/data/rule_sets/pre_registration_reapply_1783410247_95c0f3/source.xlsx
+++ b/backend/data/rule_sets/pre_registration_reapply_1783410247_95c0f3/source.xlsx
@@ -3321,10 +3321,14 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3375,17 +3379,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"产品基本信息.财产来源","op":"contains","value":"财产权"},"target":{"field":"产品基本信息.是否信托受益权转让","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
@@ -3417,7 +3421,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3798,10 +3806,14 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3852,17 +3864,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"产品基本信息.是否信托受益权转让","op":"contains_any","values":["拆分转让","整体转让"]},"target":{"field":"产品基本信息.发行、转让场所","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
@@ -3894,7 +3906,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4178,10 +4194,14 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4232,17 +4252,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"产品基本信息.发行、转让场所","op":"equals","value":"其他"},"target":{"field":"产品基本信息.发行、转让场所补充说明","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
@@ -4274,7 +4294,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4744,10 +4768,14 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4798,17 +4826,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"产品基本信息.是否为结构化信托","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
@@ -4840,7 +4868,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5213,10 +5245,14 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5267,17 +5303,17 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},{"field":"产品基本信息.项目运作模式","op":"equals","value":"封闭式"}]},"target":{"field":"产品基本信息.是否分期募集放款","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
@@ -5309,7 +5345,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -6737,10 +6777,14 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U65" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6791,17 +6835,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"业务分类信息.资产管理信托分类","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr"/>
@@ -6833,7 +6877,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -7117,10 +7165,14 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U69" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -7171,17 +7223,17 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类1","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
@@ -7213,7 +7265,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -7501,10 +7557,14 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U73" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -7555,17 +7615,17 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类2","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
@@ -7597,7 +7657,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7881,10 +7945,14 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U77" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7935,17 +8003,17 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.公益慈善信托分类","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
@@ -7977,7 +8045,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -8257,10 +8329,14 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U81" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -8311,17 +8387,17 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.是否参与资金募集","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
@@ -8353,7 +8429,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8726,10 +8806,14 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U86" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -8780,17 +8864,17 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托"]},"target":{"field":"业务分类信息.是否互联网贷款","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr"/>
@@ -8822,7 +8906,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -9102,10 +9190,14 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U90" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9156,17 +9248,17 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.是否互联网贷款","op":"equals","value":"是"},"target":{"field":"业务分类信息.业务模式","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr"/>
@@ -9198,7 +9290,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -9478,10 +9574,14 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U94" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9532,17 +9632,17 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托"]},"target":{"field":"业务分类信息.是否证券投资类信托","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr"/>
@@ -9574,7 +9674,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9850,10 +9954,14 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U98" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -9904,17 +10012,17 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托"]},"target":{"field":"业务分类信息.是否受托境外理财信托（QDII）","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr"/>
@@ -9946,7 +10054,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -10606,10 +10718,14 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U106" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -10660,17 +10776,17 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"发行规模类型","op":"equals","value":"固定规模"},"target":{"field":"交易结构.发行规模","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr"/>
@@ -10702,7 +10818,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -11552,10 +11672,14 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U116" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -11606,17 +11730,17 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"交易结构.期限类型","op":"equals","value":"固定期限"},"target":{"field":"交易结构.信托产品期限","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr"/>
@@ -11648,7 +11772,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -12219,10 +12347,14 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U123" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -12273,17 +12405,17 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"产品基本信息.登记类型","op":"equals","value":"补充预登记"},{"field":"产品基本信息.是否分期募集放款","op":"equals","value":"是"}]},"target":{"field":"交易结构.期次编号","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr"/>
@@ -12315,7 +12447,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -13949,10 +14085,14 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U141" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U141" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -14003,17 +14143,17 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"底层资产及交易对手.底层资产（二类）","op":"contains_any","values":["其他非标准化债权资产","其他非标准化金融产品"]},"target":{"field":"底层资产及交易对手.底层资产（三类）","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr"/>
@@ -14045,7 +14185,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -14904,10 +15048,14 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U151" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -14958,17 +15106,17 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"底层资产及交易对手.底层资产（二类）","op":"equals","value":"特定资产收（受）益权"},"target":{"field":"底层资产及交易对手.收（受）益权标的资产","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr"/>
@@ -15000,7 +15148,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -15280,10 +15432,14 @@
       </c>
       <c r="T155" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U155" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -15334,17 +15490,17 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"底层资产及交易对手.资产取得方式","op":"equals","value":"资金投向"},"target":{"field":"底层资产及交易对手.是否附回购","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr"/>
@@ -15376,7 +15532,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -15656,10 +15816,14 @@
       </c>
       <c r="T159" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U159" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -15710,17 +15874,17 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"底层资产及交易对手.底层资产（二类）","op":"equals","value":"贷款"},{"field":"底层资产及交易对手.资产取得方式","op":"equals","value":"资金投向"}]},"target":{"field":"底层资产及交易对手.贷款产品类别","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr"/>
@@ -15752,7 +15916,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -16032,10 +16200,14 @@
       </c>
       <c r="T163" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U163" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -16086,17 +16258,17 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},{"field":"底层资产及交易对手.底层资产（二类）","op":"equals","value":"贷款"},{"field":"底层资产及交易对手.资产取得方式","op":"equals","value":"资金投向"}]},"target":{"field":"底层资产及交易对手.是否参照委托贷款管理","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr"/>
@@ -16128,7 +16300,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -16792,10 +16968,14 @@
       </c>
       <c r="T171" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U171" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -16846,17 +17026,17 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"底层资产及交易对手.底层资产（二类）","op":"contains_any","values":["普通合伙企业份额","有限合伙企业份额"]},{"field":"底层资产及交易对手.资产取得方式","op":"equals","value":"资金投向"}]},"target":{"field":"底层资产及交易对手.合伙企业投向","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr"/>
@@ -16888,7 +17068,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -17172,10 +17356,14 @@
       </c>
       <c r="T175" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U175" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -17226,17 +17414,17 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"底层资产及交易对手.底层资产（二类）","op":"contains_any","values":["普通合伙企业份额","有限合伙企业份额"]},{"field":"底层资产及交易对手.资产取得方式","op":"equals","value":"资金投向"}]},"target":{"field":"底层资产及交易对手.合伙企业投向详情","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr"/>
@@ -17268,7 +17456,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -18122,10 +18314,14 @@
       </c>
       <c r="T185" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U185" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -18176,17 +18372,17 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"底层资产及交易对手.资产取得方式","op":"equals","value":"资金投向"},"target":{"field":"底层资产及交易对手.投向行业大类","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr"/>
@@ -18218,7 +18414,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -19630,10 +19830,14 @@
       </c>
       <c r="T201" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U201" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U201" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -19684,17 +19888,17 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"托管信息.是否聘请保（托）管人","op":"equals","value":"是"},"target":{"field":"托管信息.保（托）管人名称","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr"/>
@@ -19726,7 +19930,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -19913,10 +20121,14 @@
       </c>
       <c r="T204" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U204" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U204" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -19967,17 +20179,17 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"托管信息.是否聘请保（托）管人","op":"equals","value":"否"},{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"}]},"target":{"field":"托管信息.保障信托财产安全的措施和纠纷解决机制","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr"/>
@@ -20009,7 +20221,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -20483,10 +20699,14 @@
       </c>
       <c r="T210" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U210" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U210" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -20537,17 +20757,17 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"担保类型仅","op":"equals","value":"信用"},"target":{"field":"风险控制信息.担保人信息描述","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N211" s="2" t="inlineStr"/>
@@ -20579,7 +20799,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -20766,10 +20990,14 @@
       </c>
       <c r="T213" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U213" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U213" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -20820,17 +21048,17 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M214" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"风险控制信息.担保类型","op":"contains_any","values":["抵押","质押"]},"target":{"field":"风险控制信息.抵质押物信息描述","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N214" s="2" t="inlineStr"/>
@@ -20862,7 +21090,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -21049,10 +21281,14 @@
       </c>
       <c r="T216" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U216" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U216" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -21103,17 +21339,17 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"风险控制信息.担保类型","op":"equals","value":"保证"},"target":{"field":"风险控制信息.保证类型信息描述","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N217" s="2" t="inlineStr"/>
@@ -21145,7 +21381,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -21332,10 +21572,14 @@
       </c>
       <c r="T219" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U219" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U219" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -21386,17 +21630,17 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"风险控制信息.担保类型","op":"equals","value":"其他"},"target":{"field":"风险控制信息.其他风控信息描述","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N220" s="2" t="inlineStr"/>
@@ -21428,7 +21672,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -23131,10 +23379,14 @@
       </c>
       <c r="T238" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U238" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U238" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -23185,17 +23437,17 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M239" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"房地产项目信息.是否办理国有土地使用证","op":"equals","value":"是"},"target":{"field":"房地产项目信息.国有土地使用证号","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N239" s="2" t="inlineStr"/>
@@ -23227,7 +23479,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -23693,10 +23949,14 @@
       </c>
       <c r="T244" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U244" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U244" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -23747,17 +24007,17 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M245" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"房地产项目信息.是否办理建设用地规划许可证","op":"equals","value":"是"},"target":{"field":"房地产项目信息.建设用地规划许可证号","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N245" s="2" t="inlineStr"/>
@@ -23789,7 +24049,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -24255,10 +24519,14 @@
       </c>
       <c r="T250" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U250" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U250" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -24309,17 +24577,17 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"房地产项目信息.是否办理建设工程规划许可证","op":"equals","value":"是"},"target":{"field":"房地产项目信息.建设工程规划许可证号","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N251" s="2" t="inlineStr"/>
@@ -24351,7 +24619,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -24817,10 +25089,14 @@
       </c>
       <c r="T256" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U256" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U256" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -24871,17 +25147,17 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"房地产项目信息.是否办理建筑工程施工许可证","op":"equals","value":"是"},"target":{"field":"房地产项目信息.建筑工程施工许可证号","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N257" s="2" t="inlineStr"/>
@@ -24913,7 +25189,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -28199,10 +28479,14 @@
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="U291" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U291" s="2" t="inlineStr">
+        <is>
+          <t>已禁用：条件必填重复规则，保留同字段conditional_compare规则。</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -28253,17 +28537,17 @@
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>非空校验 + 条件逻辑判断</t>
+          <t>条件必填校验</t>
         </is>
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>conditional_compare</t>
         </is>
       </c>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>{"source_check_type":"必填非空"}</t>
+          <t>{"trigger":{"field":"关联交易事项.关联交易性质","op":"equals","value":"重大关联交易"},"target":{"field":"关联交易事项.重大关联交易是否已经董事会批准","op":"required"},"source_check_type":"必填非空"}</t>
         </is>
       </c>
       <c r="N292" s="2" t="inlineStr"/>
@@ -28295,7 +28579,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
